--- a/Encollect_Web_SCB_P3/Cypress/fixtures/ProductMasterTemplate.xlsx
+++ b/Encollect_Web_SCB_P3/Cypress/fixtures/ProductMasterTemplate.xlsx
@@ -32,11 +32,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="4">
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="@"/>
-    <numFmt numFmtId="166" formatCode="d\ mmm\ yy"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -67,9 +64,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -404,113 +400,113 @@
   <dimension ref="A1:C11"/>
   <sheetData>
     <row r="2">
-      <c r="A2" s="1" t="str">
-        <v>Clothing</v>
-      </c>
-      <c r="B2" s="1" t="str">
-        <v>Generic Bronze Ball</v>
-      </c>
-      <c r="C2" s="1" t="str">
-        <v>Unbranded</v>
+      <c r="A2" t="str">
+        <v>Outdoors</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Oriental Cotton Shoes</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Oriental</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="str">
+      <c r="A3" t="str">
+        <v>Baby</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Fantastic Fresh Sausages</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Tasty</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Movies</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Licensed Granite Bacon</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Incredible</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Computers</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Recycled Steel Table</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Recycled</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Tools</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Fantastic Wooden Ball</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Practical</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
         <v>Sports</v>
       </c>
-      <c r="B3" s="1" t="str">
-        <v>Modern Cotton Chicken</v>
-      </c>
-      <c r="C3" s="1" t="str">
-        <v>Tasty</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="str">
+      <c r="B7" t="str">
+        <v>Handmade Granite Table</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Small</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Toys</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Fantastic Cotton Keyboard</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Electronic</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Grocery</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Electronic Frozen Bacon</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Intelligent</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
         <v>Sports</v>
       </c>
-      <c r="B4" s="1" t="str">
-        <v>Small Concrete Ball</v>
-      </c>
-      <c r="C4" s="1" t="str">
-        <v>Luxurious</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="str">
-        <v>Industrial</v>
-      </c>
-      <c r="B5" s="1" t="str">
-        <v>Generic Fresh Chips</v>
-      </c>
-      <c r="C5" s="1" t="str">
-        <v>Sleek</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="str">
-        <v>Tools</v>
-      </c>
-      <c r="B6" s="1" t="str">
-        <v>Electronic Soft Shirt</v>
-      </c>
-      <c r="C6" s="1" t="str">
-        <v>Unbranded</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="str">
-        <v>Jewelry</v>
-      </c>
-      <c r="B7" s="1" t="str">
-        <v>Electronic Concrete Pizza</v>
-      </c>
-      <c r="C7" s="1" t="str">
-        <v>Handcrafted</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="str">
-        <v>Movies</v>
-      </c>
-      <c r="B8" s="1" t="str">
-        <v>Luxurious Granite Chair</v>
-      </c>
-      <c r="C8" s="1" t="str">
+      <c r="B10" t="str">
+        <v>Generic Concrete Salad</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Fantastic</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Games</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Sleek Bronze Soap</v>
+      </c>
+      <c r="C11" t="str">
         <v>Elegant</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="str">
-        <v>Home</v>
-      </c>
-      <c r="B9" s="1" t="str">
-        <v>Unbranded Concrete Sausages</v>
-      </c>
-      <c r="C9" s="1" t="str">
-        <v>Oriental</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="str">
-        <v>Health</v>
-      </c>
-      <c r="B10" s="1" t="str">
-        <v>Fantastic Metal Shirt</v>
-      </c>
-      <c r="C10" s="1" t="str">
-        <v>Generic</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="str">
-        <v>Kids</v>
-      </c>
-      <c r="B11" s="1" t="str">
-        <v>Electronic Metal Keyboard</v>
-      </c>
-      <c r="C11" s="1" t="str">
-        <v>Practical</v>
       </c>
     </row>
   </sheetData>

--- a/Encollect_Web_SCB_P3/Cypress/fixtures/ProductMasterTemplate.xlsx
+++ b/Encollect_Web_SCB_P3/Cypress/fixtures/ProductMasterTemplate.xlsx
@@ -404,109 +404,109 @@
         <v>Outdoors</v>
       </c>
       <c r="B2" t="str">
-        <v>Oriental Cotton Shoes</v>
+        <v>Ergonomic Bronze Gloves</v>
       </c>
       <c r="C2" t="str">
-        <v>Oriental</v>
+        <v>Elegant</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Baby</v>
+        <v>Games</v>
       </c>
       <c r="B3" t="str">
-        <v>Fantastic Fresh Sausages</v>
+        <v>Bespoke Cotton Chips</v>
       </c>
       <c r="C3" t="str">
-        <v>Tasty</v>
+        <v>Handcrafted</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Movies</v>
+        <v>Home</v>
       </c>
       <c r="B4" t="str">
-        <v>Licensed Granite Bacon</v>
+        <v>Small Soft Car</v>
       </c>
       <c r="C4" t="str">
-        <v>Incredible</v>
+        <v>Fantastic</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Computers</v>
+        <v>Books</v>
       </c>
       <c r="B5" t="str">
-        <v>Recycled Steel Table</v>
+        <v>Practical Granite Hat</v>
       </c>
       <c r="C5" t="str">
-        <v>Recycled</v>
+        <v>Oriental</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Tools</v>
+        <v>Industrial</v>
       </c>
       <c r="B6" t="str">
-        <v>Fantastic Wooden Ball</v>
+        <v>Bespoke Fresh Computer</v>
       </c>
       <c r="C6" t="str">
-        <v>Practical</v>
+        <v>Generic</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Sports</v>
+        <v>Home</v>
       </c>
       <c r="B7" t="str">
-        <v>Handmade Granite Table</v>
+        <v>Unbranded Bronze Soap</v>
       </c>
       <c r="C7" t="str">
-        <v>Small</v>
+        <v>Tasty</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Toys</v>
+        <v>Books</v>
       </c>
       <c r="B8" t="str">
-        <v>Fantastic Cotton Keyboard</v>
+        <v>Handmade Granite Table</v>
       </c>
       <c r="C8" t="str">
-        <v>Electronic</v>
+        <v>Sleek</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Grocery</v>
+        <v>Computers</v>
       </c>
       <c r="B9" t="str">
-        <v>Electronic Frozen Bacon</v>
+        <v>Unbranded Plastic Salad</v>
       </c>
       <c r="C9" t="str">
-        <v>Intelligent</v>
+        <v>Handmade</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Sports</v>
+        <v>Garden</v>
       </c>
       <c r="B10" t="str">
-        <v>Generic Concrete Salad</v>
+        <v>Incredible Steel Tuna</v>
       </c>
       <c r="C10" t="str">
-        <v>Fantastic</v>
+        <v>Handmade</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Games</v>
+        <v>Toys</v>
       </c>
       <c r="B11" t="str">
-        <v>Sleek Bronze Soap</v>
+        <v>Practical Plastic Fish</v>
       </c>
       <c r="C11" t="str">
-        <v>Elegant</v>
+        <v>Small</v>
       </c>
     </row>
   </sheetData>

--- a/Encollect_Web_SCB_P3/Cypress/fixtures/ProductMasterTemplate.xlsx
+++ b/Encollect_Web_SCB_P3/Cypress/fixtures/ProductMasterTemplate.xlsx
@@ -401,21 +401,21 @@
   <sheetData>
     <row r="2">
       <c r="A2" t="str">
-        <v>Outdoors</v>
+        <v>Electronics</v>
       </c>
       <c r="B2" t="str">
-        <v>Ergonomic Bronze Gloves</v>
+        <v>Bespoke Bronze Pants</v>
       </c>
       <c r="C2" t="str">
-        <v>Elegant</v>
+        <v>Gorgeous</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Games</v>
+        <v>Home</v>
       </c>
       <c r="B3" t="str">
-        <v>Bespoke Cotton Chips</v>
+        <v>Recycled Granite Bacon</v>
       </c>
       <c r="C3" t="str">
         <v>Handcrafted</v>
@@ -423,35 +423,35 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Home</v>
+        <v>Garden</v>
       </c>
       <c r="B4" t="str">
-        <v>Small Soft Car</v>
+        <v>Refined Ceramic Tuna</v>
       </c>
       <c r="C4" t="str">
-        <v>Fantastic</v>
+        <v>Bespoke</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Books</v>
+        <v>Music</v>
       </c>
       <c r="B5" t="str">
-        <v>Practical Granite Hat</v>
+        <v>Modern Cotton Bacon</v>
       </c>
       <c r="C5" t="str">
-        <v>Oriental</v>
+        <v>Awesome</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Industrial</v>
+        <v>Health</v>
       </c>
       <c r="B6" t="str">
-        <v>Bespoke Fresh Computer</v>
+        <v>Bespoke Concrete Chicken</v>
       </c>
       <c r="C6" t="str">
-        <v>Generic</v>
+        <v>Awesome</v>
       </c>
     </row>
     <row r="7">
@@ -459,54 +459,54 @@
         <v>Home</v>
       </c>
       <c r="B7" t="str">
-        <v>Unbranded Bronze Soap</v>
+        <v>Practical Metal Sausages</v>
       </c>
       <c r="C7" t="str">
-        <v>Tasty</v>
+        <v>Soft</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Books</v>
+        <v>Jewelry</v>
       </c>
       <c r="B8" t="str">
-        <v>Handmade Granite Table</v>
+        <v>Intelligent Plastic Chicken</v>
       </c>
       <c r="C8" t="str">
-        <v>Sleek</v>
+        <v>Unbranded</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Computers</v>
+        <v>Electronics</v>
       </c>
       <c r="B9" t="str">
-        <v>Unbranded Plastic Salad</v>
+        <v>Awesome Steel Towels</v>
       </c>
       <c r="C9" t="str">
-        <v>Handmade</v>
+        <v>Sleek</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Garden</v>
+        <v>Books</v>
       </c>
       <c r="B10" t="str">
-        <v>Incredible Steel Tuna</v>
+        <v>Electronic Plastic Shoes</v>
       </c>
       <c r="C10" t="str">
-        <v>Handmade</v>
+        <v>Soft</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Toys</v>
+        <v>Garden</v>
       </c>
       <c r="B11" t="str">
-        <v>Practical Plastic Fish</v>
+        <v>Handcrafted Plastic Soap</v>
       </c>
       <c r="C11" t="str">
-        <v>Small</v>
+        <v>Sleek</v>
       </c>
     </row>
   </sheetData>

--- a/Encollect_Web_SCB_P3/Cypress/fixtures/ProductMasterTemplate.xlsx
+++ b/Encollect_Web_SCB_P3/Cypress/fixtures/ProductMasterTemplate.xlsx
@@ -401,112 +401,112 @@
   <sheetData>
     <row r="2">
       <c r="A2" t="str">
-        <v>Electronics</v>
+        <v>Kids</v>
       </c>
       <c r="B2" t="str">
-        <v>Bespoke Bronze Pants</v>
+        <v>Incredible Bamboo Towels</v>
       </c>
       <c r="C2" t="str">
-        <v>Gorgeous</v>
+        <v>Intelligent</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Home</v>
+        <v>Books</v>
       </c>
       <c r="B3" t="str">
-        <v>Recycled Granite Bacon</v>
+        <v>Handcrafted Marble Tuna</v>
       </c>
       <c r="C3" t="str">
-        <v>Handcrafted</v>
+        <v>Bespoke</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Garden</v>
+        <v>Tools</v>
       </c>
       <c r="B4" t="str">
-        <v>Refined Ceramic Tuna</v>
+        <v>Sleek Bronze Sausages</v>
       </c>
       <c r="C4" t="str">
-        <v>Bespoke</v>
+        <v>Ergonomic</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Music</v>
+        <v>Toys</v>
       </c>
       <c r="B5" t="str">
-        <v>Modern Cotton Bacon</v>
+        <v>Incredible Bronze Chips</v>
       </c>
       <c r="C5" t="str">
-        <v>Awesome</v>
+        <v>Unbranded</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Health</v>
+        <v>Games</v>
       </c>
       <c r="B6" t="str">
-        <v>Bespoke Concrete Chicken</v>
+        <v>Elegant Bamboo Table</v>
       </c>
       <c r="C6" t="str">
-        <v>Awesome</v>
+        <v>Rustic</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Home</v>
+        <v>Books</v>
       </c>
       <c r="B7" t="str">
-        <v>Practical Metal Sausages</v>
+        <v>Licensed Plastic Mouse</v>
       </c>
       <c r="C7" t="str">
-        <v>Soft</v>
+        <v>Elegant</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Jewelry</v>
+        <v>Clothing</v>
       </c>
       <c r="B8" t="str">
-        <v>Intelligent Plastic Chicken</v>
+        <v>Oriental Bronze Shoes</v>
       </c>
       <c r="C8" t="str">
-        <v>Unbranded</v>
+        <v>Luxurious</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Electronics</v>
+        <v>Music</v>
       </c>
       <c r="B9" t="str">
-        <v>Awesome Steel Towels</v>
+        <v>Intelligent Ceramic Soap</v>
       </c>
       <c r="C9" t="str">
-        <v>Sleek</v>
+        <v>Unbranded</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Books</v>
+        <v>Kids</v>
       </c>
       <c r="B10" t="str">
-        <v>Electronic Plastic Shoes</v>
+        <v>Handmade Rubber Towels</v>
       </c>
       <c r="C10" t="str">
-        <v>Soft</v>
+        <v>Modern</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Garden</v>
+        <v>Toys</v>
       </c>
       <c r="B11" t="str">
-        <v>Handcrafted Plastic Soap</v>
+        <v>Intelligent Marble Pants</v>
       </c>
       <c r="C11" t="str">
-        <v>Sleek</v>
+        <v>Small</v>
       </c>
     </row>
   </sheetData>

--- a/Encollect_Web_SCB_P3/Cypress/fixtures/ProductMasterTemplate.xlsx
+++ b/Encollect_Web_SCB_P3/Cypress/fixtures/ProductMasterTemplate.xlsx
@@ -401,112 +401,112 @@
   <sheetData>
     <row r="2">
       <c r="A2" t="str">
-        <v>Kids</v>
+        <v>Movies</v>
       </c>
       <c r="B2" t="str">
-        <v>Incredible Bamboo Towels</v>
+        <v>Practical Rubber Salad</v>
       </c>
       <c r="C2" t="str">
-        <v>Intelligent</v>
+        <v>Practical</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Books</v>
+        <v>Grocery</v>
       </c>
       <c r="B3" t="str">
-        <v>Handcrafted Marble Tuna</v>
+        <v>Modern Silk Salad</v>
       </c>
       <c r="C3" t="str">
-        <v>Bespoke</v>
+        <v>Awesome</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Tools</v>
+        <v>Toys</v>
       </c>
       <c r="B4" t="str">
-        <v>Sleek Bronze Sausages</v>
+        <v>Elegant Rubber Keyboard</v>
       </c>
       <c r="C4" t="str">
-        <v>Ergonomic</v>
+        <v>Fantastic</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Toys</v>
+        <v>Beauty</v>
       </c>
       <c r="B5" t="str">
-        <v>Incredible Bronze Chips</v>
+        <v>Sleek Ceramic Tuna</v>
       </c>
       <c r="C5" t="str">
-        <v>Unbranded</v>
+        <v>Bespoke</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Games</v>
+        <v>Beauty</v>
       </c>
       <c r="B6" t="str">
-        <v>Elegant Bamboo Table</v>
+        <v>Incredible Rubber Bike</v>
       </c>
       <c r="C6" t="str">
-        <v>Rustic</v>
+        <v>Elegant</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Books</v>
+        <v>Music</v>
       </c>
       <c r="B7" t="str">
-        <v>Licensed Plastic Mouse</v>
+        <v>Gorgeous Ceramic Cheese</v>
       </c>
       <c r="C7" t="str">
-        <v>Elegant</v>
+        <v>Unbranded</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Clothing</v>
+        <v>Automotive</v>
       </c>
       <c r="B8" t="str">
-        <v>Oriental Bronze Shoes</v>
+        <v>Awesome Bamboo Chair</v>
       </c>
       <c r="C8" t="str">
-        <v>Luxurious</v>
+        <v>Ergonomic</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Music</v>
+        <v>Electronics</v>
       </c>
       <c r="B9" t="str">
-        <v>Intelligent Ceramic Soap</v>
+        <v>Incredible Bamboo Sausages</v>
       </c>
       <c r="C9" t="str">
-        <v>Unbranded</v>
+        <v>Recycled</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Kids</v>
+        <v>Toys</v>
       </c>
       <c r="B10" t="str">
-        <v>Handmade Rubber Towels</v>
+        <v>Fantastic Marble Shirt</v>
       </c>
       <c r="C10" t="str">
-        <v>Modern</v>
+        <v>Incredible</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Toys</v>
+        <v>Outdoors</v>
       </c>
       <c r="B11" t="str">
-        <v>Intelligent Marble Pants</v>
+        <v>Electronic Ceramic Bacon</v>
       </c>
       <c r="C11" t="str">
-        <v>Small</v>
+        <v>Generic</v>
       </c>
     </row>
   </sheetData>

--- a/Encollect_Web_SCB_P3/Cypress/fixtures/ProductMasterTemplate.xlsx
+++ b/Encollect_Web_SCB_P3/Cypress/fixtures/ProductMasterTemplate.xlsx
@@ -401,112 +401,112 @@
   <sheetData>
     <row r="2">
       <c r="A2" t="str">
-        <v>Movies</v>
+        <v>Outdoors</v>
       </c>
       <c r="B2" t="str">
-        <v>Practical Rubber Salad</v>
+        <v>Elegant Wooden Bike</v>
       </c>
       <c r="C2" t="str">
-        <v>Practical</v>
+        <v>Small</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Grocery</v>
+        <v>Baby</v>
       </c>
       <c r="B3" t="str">
-        <v>Modern Silk Salad</v>
+        <v>Soft Granite Salad</v>
       </c>
       <c r="C3" t="str">
-        <v>Awesome</v>
+        <v>Handmade</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Toys</v>
+        <v>Games</v>
       </c>
       <c r="B4" t="str">
-        <v>Elegant Rubber Keyboard</v>
+        <v>Intelligent Gold Pants</v>
       </c>
       <c r="C4" t="str">
-        <v>Fantastic</v>
+        <v>Awesome</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Beauty</v>
+        <v>Jewelry</v>
       </c>
       <c r="B5" t="str">
-        <v>Sleek Ceramic Tuna</v>
+        <v>Bespoke Aluminum Salad</v>
       </c>
       <c r="C5" t="str">
-        <v>Bespoke</v>
+        <v>Tasty</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Beauty</v>
+        <v>Home</v>
       </c>
       <c r="B6" t="str">
-        <v>Incredible Rubber Bike</v>
+        <v>Soft Wooden Car</v>
       </c>
       <c r="C6" t="str">
-        <v>Elegant</v>
+        <v>Generic</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Music</v>
+        <v>Electronics</v>
       </c>
       <c r="B7" t="str">
-        <v>Gorgeous Ceramic Cheese</v>
+        <v>Luxurious Marble Computer</v>
       </c>
       <c r="C7" t="str">
-        <v>Unbranded</v>
+        <v>Sleek</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Automotive</v>
+        <v>Games</v>
       </c>
       <c r="B8" t="str">
-        <v>Awesome Bamboo Chair</v>
+        <v>Bespoke Rubber Ball</v>
       </c>
       <c r="C8" t="str">
-        <v>Ergonomic</v>
+        <v>Luxurious</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Electronics</v>
+        <v>Books</v>
       </c>
       <c r="B9" t="str">
-        <v>Incredible Bamboo Sausages</v>
+        <v>Elegant Silk Car</v>
       </c>
       <c r="C9" t="str">
-        <v>Recycled</v>
+        <v>Fresh</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Toys</v>
+        <v>Books</v>
       </c>
       <c r="B10" t="str">
-        <v>Fantastic Marble Shirt</v>
+        <v>Unbranded Granite Pants</v>
       </c>
       <c r="C10" t="str">
-        <v>Incredible</v>
+        <v>Generic</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Outdoors</v>
+        <v>Automotive</v>
       </c>
       <c r="B11" t="str">
-        <v>Electronic Ceramic Bacon</v>
+        <v>Fantastic Bronze Sausages</v>
       </c>
       <c r="C11" t="str">
-        <v>Generic</v>
+        <v>Handmade</v>
       </c>
     </row>
   </sheetData>

--- a/Encollect_Web_SCB_P3/Cypress/fixtures/ProductMasterTemplate.xlsx
+++ b/Encollect_Web_SCB_P3/Cypress/fixtures/ProductMasterTemplate.xlsx
@@ -404,109 +404,109 @@
         <v>Outdoors</v>
       </c>
       <c r="B2" t="str">
-        <v>Elegant Wooden Bike</v>
+        <v>Fantastic Cotton Chips</v>
       </c>
       <c r="C2" t="str">
-        <v>Small</v>
+        <v>Recycled</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Baby</v>
+        <v>Home</v>
       </c>
       <c r="B3" t="str">
-        <v>Soft Granite Salad</v>
+        <v>Bespoke Metal Towels</v>
       </c>
       <c r="C3" t="str">
-        <v>Handmade</v>
+        <v>Sleek</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Games</v>
+        <v>Music</v>
       </c>
       <c r="B4" t="str">
-        <v>Intelligent Gold Pants</v>
+        <v>Oriental Marble Ball</v>
       </c>
       <c r="C4" t="str">
-        <v>Awesome</v>
+        <v>Unbranded</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Jewelry</v>
+        <v>Sports</v>
       </c>
       <c r="B5" t="str">
-        <v>Bespoke Aluminum Salad</v>
+        <v>Recycled Granite Computer</v>
       </c>
       <c r="C5" t="str">
-        <v>Tasty</v>
+        <v>Frozen</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Home</v>
+        <v>Clothing</v>
       </c>
       <c r="B6" t="str">
-        <v>Soft Wooden Car</v>
+        <v>Practical Aluminum Soap</v>
       </c>
       <c r="C6" t="str">
-        <v>Generic</v>
+        <v>Oriental</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Electronics</v>
+        <v>Garden</v>
       </c>
       <c r="B7" t="str">
-        <v>Luxurious Marble Computer</v>
+        <v>Handmade Concrete Keyboard</v>
       </c>
       <c r="C7" t="str">
-        <v>Sleek</v>
+        <v>Fresh</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Games</v>
+        <v>Baby</v>
       </c>
       <c r="B8" t="str">
-        <v>Bespoke Rubber Ball</v>
+        <v>Rustic Rubber Salad</v>
       </c>
       <c r="C8" t="str">
-        <v>Luxurious</v>
+        <v>Rustic</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Books</v>
+        <v>Electronics</v>
       </c>
       <c r="B9" t="str">
-        <v>Elegant Silk Car</v>
+        <v>Frozen Plastic Towels</v>
       </c>
       <c r="C9" t="str">
-        <v>Fresh</v>
+        <v>Rustic</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Books</v>
+        <v>Health</v>
       </c>
       <c r="B10" t="str">
-        <v>Unbranded Granite Pants</v>
+        <v>Incredible Plastic Cheese</v>
       </c>
       <c r="C10" t="str">
-        <v>Generic</v>
+        <v>Electronic</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Automotive</v>
+        <v>Computers</v>
       </c>
       <c r="B11" t="str">
-        <v>Fantastic Bronze Sausages</v>
+        <v>Licensed Bamboo Chair</v>
       </c>
       <c r="C11" t="str">
-        <v>Handmade</v>
+        <v>Elegant</v>
       </c>
     </row>
   </sheetData>

--- a/Encollect_Web_SCB_P3/Cypress/fixtures/ProductMasterTemplate.xlsx
+++ b/Encollect_Web_SCB_P3/Cypress/fixtures/ProductMasterTemplate.xlsx
@@ -401,112 +401,112 @@
   <sheetData>
     <row r="2">
       <c r="A2" t="str">
-        <v>Outdoors</v>
+        <v>Toys</v>
       </c>
       <c r="B2" t="str">
-        <v>Fantastic Cotton Chips</v>
+        <v>Gorgeous Cotton Ball</v>
       </c>
       <c r="C2" t="str">
-        <v>Recycled</v>
+        <v>Oriental</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Home</v>
+        <v>Sports</v>
       </c>
       <c r="B3" t="str">
-        <v>Bespoke Metal Towels</v>
+        <v>Tasty Cotton Tuna</v>
       </c>
       <c r="C3" t="str">
-        <v>Sleek</v>
+        <v>Luxurious</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Music</v>
+        <v>Computers</v>
       </c>
       <c r="B4" t="str">
-        <v>Oriental Marble Ball</v>
+        <v>Ergonomic Granite Keyboard</v>
       </c>
       <c r="C4" t="str">
-        <v>Unbranded</v>
+        <v>Sleek</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Sports</v>
+        <v>Health</v>
       </c>
       <c r="B5" t="str">
-        <v>Recycled Granite Computer</v>
+        <v>Sleek Marble Towels</v>
       </c>
       <c r="C5" t="str">
-        <v>Frozen</v>
+        <v>Rustic</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Clothing</v>
+        <v>Industrial</v>
       </c>
       <c r="B6" t="str">
-        <v>Practical Aluminum Soap</v>
+        <v>Soft Rubber Towels</v>
       </c>
       <c r="C6" t="str">
-        <v>Oriental</v>
+        <v>Unbranded</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Garden</v>
+        <v>Music</v>
       </c>
       <c r="B7" t="str">
-        <v>Handmade Concrete Keyboard</v>
+        <v>Recycled Bamboo Towels</v>
       </c>
       <c r="C7" t="str">
-        <v>Fresh</v>
+        <v>Bespoke</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Baby</v>
+        <v>Kids</v>
       </c>
       <c r="B8" t="str">
-        <v>Rustic Rubber Salad</v>
+        <v>Gorgeous Bamboo Chips</v>
       </c>
       <c r="C8" t="str">
-        <v>Rustic</v>
+        <v>Handcrafted</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Electronics</v>
+        <v>Computers</v>
       </c>
       <c r="B9" t="str">
-        <v>Frozen Plastic Towels</v>
+        <v>Luxurious Bamboo Fish</v>
       </c>
       <c r="C9" t="str">
-        <v>Rustic</v>
+        <v>Fantastic</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Health</v>
+        <v>Toys</v>
       </c>
       <c r="B10" t="str">
-        <v>Incredible Plastic Cheese</v>
+        <v>Generic Aluminum Fish</v>
       </c>
       <c r="C10" t="str">
-        <v>Electronic</v>
+        <v>Elegant</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Computers</v>
+        <v>Jewelry</v>
       </c>
       <c r="B11" t="str">
-        <v>Licensed Bamboo Chair</v>
+        <v>Oriental Granite Chair</v>
       </c>
       <c r="C11" t="str">
-        <v>Elegant</v>
+        <v>Handcrafted</v>
       </c>
     </row>
   </sheetData>

--- a/Encollect_Web_SCB_P3/Cypress/fixtures/ProductMasterTemplate.xlsx
+++ b/Encollect_Web_SCB_P3/Cypress/fixtures/ProductMasterTemplate.xlsx
@@ -32,8 +32,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="4">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="@"/>
+    <numFmt numFmtId="166" formatCode="d\ mmm\ yy"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -64,8 +67,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -400,113 +404,113 @@
   <dimension ref="A1:C11"/>
   <sheetData>
     <row r="2">
-      <c r="A2" t="str">
+      <c r="A2" s="1" t="str">
+        <v>Beauty</v>
+      </c>
+      <c r="B2" s="1" t="str">
+        <v>Refined Plastic Soap</v>
+      </c>
+      <c r="C2" s="1" t="str">
+        <v>Oriental</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="str">
+        <v>Books</v>
+      </c>
+      <c r="B3" s="1" t="str">
+        <v>Soft Marble Chicken</v>
+      </c>
+      <c r="C3" s="1" t="str">
+        <v>Bespoke</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="str">
         <v>Toys</v>
       </c>
-      <c r="B2" t="str">
-        <v>Gorgeous Cotton Ball</v>
-      </c>
-      <c r="C2" t="str">
+      <c r="B4" s="1" t="str">
+        <v>Generic Wooden Towels</v>
+      </c>
+      <c r="C4" s="1" t="str">
+        <v>Handcrafted</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="str">
+        <v>Jewelry</v>
+      </c>
+      <c r="B5" s="1" t="str">
+        <v>Soft Silk Salad</v>
+      </c>
+      <c r="C5" s="1" t="str">
+        <v>Licensed</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="str">
+        <v>Tools</v>
+      </c>
+      <c r="B6" s="1" t="str">
+        <v>Luxurious Bronze Salad</v>
+      </c>
+      <c r="C6" s="1" t="str">
+        <v>Incredible</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="str">
+        <v>Computers</v>
+      </c>
+      <c r="B7" s="1" t="str">
+        <v>Soft Gold Ball</v>
+      </c>
+      <c r="C7" s="1" t="str">
+        <v>Luxurious</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="str">
+        <v>Electronics</v>
+      </c>
+      <c r="B8" s="1" t="str">
+        <v>Unbranded Wooden Shoes</v>
+      </c>
+      <c r="C8" s="1" t="str">
         <v>Oriental</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Sports</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Tasty Cotton Tuna</v>
-      </c>
-      <c r="C3" t="str">
+    <row r="9">
+      <c r="A9" s="1" t="str">
+        <v>Books</v>
+      </c>
+      <c r="B9" s="1" t="str">
+        <v>Small Bronze Gloves</v>
+      </c>
+      <c r="C9" s="1" t="str">
+        <v>Electronic</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="str">
+        <v>Health</v>
+      </c>
+      <c r="B10" s="1" t="str">
+        <v>Ergonomic Silk Chips</v>
+      </c>
+      <c r="C10" s="1" t="str">
         <v>Luxurious</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Computers</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Ergonomic Granite Keyboard</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Sleek</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Health</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Sleek Marble Towels</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Rustic</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
+    <row r="11">
+      <c r="A11" s="1" t="str">
         <v>Industrial</v>
       </c>
-      <c r="B6" t="str">
-        <v>Soft Rubber Towels</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Unbranded</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Music</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Recycled Bamboo Towels</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Bespoke</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Kids</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Gorgeous Bamboo Chips</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Handcrafted</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Computers</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Luxurious Bamboo Fish</v>
-      </c>
-      <c r="C9" t="str">
-        <v>Fantastic</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Toys</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Generic Aluminum Fish</v>
-      </c>
-      <c r="C10" t="str">
-        <v>Elegant</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Jewelry</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Oriental Granite Chair</v>
-      </c>
-      <c r="C11" t="str">
-        <v>Handcrafted</v>
+      <c r="B11" s="1" t="str">
+        <v>Luxurious Marble Sausages</v>
+      </c>
+      <c r="C11" s="1" t="str">
+        <v>Practical</v>
       </c>
     </row>
   </sheetData>
